--- a/data-source/符文数据.xlsx
+++ b/data-source/符文数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C72B19-C21D-4086-8A52-4345AE2C90D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D3943D-5253-4BF2-B4B8-93E6CBA7BCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
     <t>恐惧符文</t>
   </si>
   <si>
-    <t>放置地面激活是使敌人陷入恐惧，他有5次次数</t>
+    <t>放置地面，激活使敌人陷入恐惧同时造成30点额外伤害，他有10次充能次数</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -128,6 +128,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,11 +443,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="27">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
     </row>
